--- a/Assets/GameResource/Excel/触发事件权重配置（未配置.xlsx
+++ b/Assets/GameResource/Excel/触发事件权重配置（未配置.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\Demo\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFFF1C8-C0FB-4F36-836B-EA0786FFA389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA38586-11BA-490F-AEC7-30E46D77333C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="466" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="TriggerEventRandomConfig" sheetId="1" r:id="rId1"/>
+    <sheet name="GridTriggerWeight" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,73 +44,80 @@
     <t>DifficultId</t>
   </si>
   <si>
-    <t>NormalCombatRoomRandomList</t>
-  </si>
-  <si>
-    <t>EliteCombatRoomRandomList</t>
-  </si>
-  <si>
     <t>TreasureRoomWeight</t>
   </si>
   <si>
+    <t>BossRoom</t>
+  </si>
+  <si>
+    <t>HealthIncreaseParam</t>
+  </si>
+  <si>
+    <t>AttackIncreaseParam</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>自增id</t>
+  </si>
+  <si>
+    <t>编号id</t>
+  </si>
+  <si>
+    <t>难度id</t>
+  </si>
+  <si>
+    <t>Boss房间id</t>
+  </si>
+  <si>
+    <t>生命值增幅系数</t>
+  </si>
+  <si>
+    <t>攻击力增幅系数</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5</t>
+  </si>
+  <si>
+    <t>6,7,8,9</t>
+  </si>
+  <si>
+    <t>15,15,15,15,15,16,16,16,17,17</t>
+  </si>
+  <si>
+    <t>15,15,15,15,15,16,16,16,17,17</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝箱格子权重</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>TreasureRoomList</t>
-  </si>
-  <si>
-    <t>BossRoom</t>
-  </si>
-  <si>
-    <t>HealthIncreaseParam</t>
-  </si>
-  <si>
-    <t>AttackIncreaseParam</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>自增id</t>
-  </si>
-  <si>
-    <t>编号id</t>
-  </si>
-  <si>
-    <t>难度id</t>
-  </si>
-  <si>
-    <t>普通房间随机List</t>
-  </si>
-  <si>
-    <t>精英房间随机List</t>
-  </si>
-  <si>
-    <t>宝箱房间权重</t>
-  </si>
-  <si>
-    <t>宝箱房间id List</t>
-  </si>
-  <si>
-    <t>Boss房间id</t>
-  </si>
-  <si>
-    <t>生命值增幅系数</t>
-  </si>
-  <si>
-    <t>攻击力增幅系数</t>
-  </si>
-  <si>
-    <t>1,2,3,4,5</t>
-  </si>
-  <si>
-    <t>6,7,8,9</t>
-  </si>
-  <si>
-    <t>15,15,15,15,15,16,16,16,17,17</t>
-  </si>
-  <si>
-    <t>15,15,15,15,15,16,16,16,17,17</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝箱抽取权重</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EliteGrid</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NormalGrid</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通敌人遭遇</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>精英敌人遭遇</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -472,90 +479,90 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -569,10 +576,10 @@
         <v>1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -595,16 +602,16 @@
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F5">
         <v>50</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -624,16 +631,16 @@
         <v>1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F6">
         <v>50</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -653,16 +660,16 @@
         <v>1</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F7">
         <v>50</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -682,16 +689,16 @@
         <v>1</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F8">
         <v>50</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -711,16 +718,16 @@
         <v>1</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F9">
         <v>50</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -740,16 +747,16 @@
         <v>1</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F10">
         <v>50</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I10">
         <v>1</v>
